--- a/reports/Debug-snowbowl-20251216/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/For Winter Ending (Prior Year)_Visits.xlsx
@@ -34,10 +34,10 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
     <t>Snowbowl Tickets</t>
@@ -434,7 +434,7 @@
         <v>45604</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C4" s="2">
-        <v>26</v>
+        <v>512</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45609</v>
+        <v>45607</v>
       </c>
       <c r="C5" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45610</v>
+        <v>45607</v>
       </c>
       <c r="C6" s="2">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,13 +501,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45612</v>
+        <v>45608</v>
       </c>
       <c r="C7" s="2">
-        <v>456</v>
+        <v>235</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45613</v>
+        <v>45611</v>
       </c>
       <c r="C8" s="2">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45614</v>
+        <v>45612</v>
       </c>
       <c r="C9" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C10" s="2">
-        <v>320</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45615</v>
+        <v>45618</v>
       </c>
       <c r="C11" s="2">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,10 +571,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45616</v>
+        <v>45621</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -585,10 +585,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45616</v>
+        <v>45621</v>
       </c>
       <c r="C13" s="2">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -599,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45617</v>
+        <v>45623</v>
       </c>
       <c r="C14" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -613,10 +613,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45617</v>
+        <v>45624</v>
       </c>
       <c r="C15" s="2">
-        <v>272</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45618</v>
+        <v>45624</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>824</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45618</v>
+        <v>45626</v>
       </c>
       <c r="C17" s="2">
-        <v>482</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,10 +655,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45619</v>
+        <v>45626</v>
       </c>
       <c r="C18" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -669,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45620</v>
+        <v>45627</v>
       </c>
       <c r="C19" s="2">
-        <v>43</v>
+        <v>786</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45620</v>
+        <v>45627</v>
       </c>
       <c r="C20" s="2">
-        <v>670</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,10 +697,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45621</v>
+        <v>45628</v>
       </c>
       <c r="C21" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -711,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45621</v>
+        <v>45629</v>
       </c>
       <c r="C22" s="2">
-        <v>529</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45622</v>
+        <v>45630</v>
       </c>
       <c r="C23" s="2">
-        <v>9</v>
+        <v>485</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="C24" s="2">
-        <v>608</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,10 +753,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45624</v>
+        <v>45631</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -767,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45625</v>
+        <v>45633</v>
       </c>
       <c r="C26" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -781,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45625</v>
+        <v>45633</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>1404</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45627</v>
+        <v>45633</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45629</v>
+        <v>45634</v>
       </c>
       <c r="C29" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C30" s="2">
-        <v>60</v>
+        <v>854</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -837,10 +837,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C31" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C32" s="2">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -865,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45638</v>
+        <v>45637</v>
       </c>
       <c r="C33" s="2">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C34" s="2">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,7 +896,7 @@
         <v>45640</v>
       </c>
       <c r="C35" s="2">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C36" s="2">
-        <v>1165</v>
+        <v>829</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45642</v>
+        <v>45641</v>
       </c>
       <c r="C37" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45604</v>
+        <v>45641</v>
       </c>
       <c r="C38" s="2">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,7 +952,7 @@
         <v>45604</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,10 +966,10 @@
         <v>45604</v>
       </c>
       <c r="C40" s="2">
-        <v>139</v>
+        <v>789</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,10 +977,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45607</v>
+        <v>45605</v>
       </c>
       <c r="C41" s="2">
-        <v>473</v>
+        <v>237</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -991,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45608</v>
+        <v>45606</v>
       </c>
       <c r="C42" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45610</v>
+        <v>45607</v>
       </c>
       <c r="C43" s="2">
-        <v>120</v>
+        <v>904</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45611</v>
+        <v>45609</v>
       </c>
       <c r="C44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45613</v>
+        <v>45616</v>
       </c>
       <c r="C45" s="2">
-        <v>468</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45614</v>
+        <v>45619</v>
       </c>
       <c r="C46" s="2">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,10 +1061,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45616</v>
+        <v>45622</v>
       </c>
       <c r="C47" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1075,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="C48" s="2">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C49" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,10 +1103,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45619</v>
+        <v>45625</v>
       </c>
       <c r="C50" s="2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1117,10 +1117,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45621</v>
+        <v>45625</v>
       </c>
       <c r="C51" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>7</v>
@@ -1131,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45622</v>
+        <v>45625</v>
       </c>
       <c r="C52" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1145,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45622</v>
+        <v>45626</v>
       </c>
       <c r="C53" s="2">
-        <v>415</v>
+        <v>302</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,10 +1159,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="C54" s="2">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1173,10 +1173,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1187,13 +1187,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45624</v>
+        <v>45628</v>
       </c>
       <c r="C56" s="2">
-        <v>7</v>
+        <v>476</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45624</v>
+        <v>45629</v>
       </c>
       <c r="C57" s="2">
-        <v>326</v>
+        <v>29</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1215,10 +1215,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45625</v>
+        <v>45630</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1229,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45625</v>
+        <v>45630</v>
       </c>
       <c r="C59" s="2">
-        <v>25</v>
+        <v>416</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1243,13 +1243,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45625</v>
+        <v>45631</v>
       </c>
       <c r="C60" s="2">
-        <v>935</v>
+        <v>383</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1257,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45627</v>
+        <v>45632</v>
       </c>
       <c r="C61" s="2">
         <v>7</v>
@@ -1271,13 +1271,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45628</v>
+        <v>45632</v>
       </c>
       <c r="C62" s="2">
-        <v>388</v>
+        <v>50</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1285,10 +1285,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C63" s="2">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1299,10 +1299,10 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45631</v>
+        <v>45633</v>
       </c>
       <c r="C64" s="2">
-        <v>376</v>
+        <v>881</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1313,10 +1313,10 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C65" s="2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1327,10 +1327,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45636</v>
+        <v>45634</v>
       </c>
       <c r="C66" s="2">
-        <v>642</v>
+        <v>945</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
@@ -1341,13 +1341,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45637</v>
+        <v>45635</v>
       </c>
       <c r="C67" s="2">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1355,10 +1355,10 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45639</v>
+        <v>45636</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>338</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1369,13 +1369,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C69" s="2">
-        <v>807</v>
+        <v>2</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1383,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C70" s="2">
-        <v>192</v>
+        <v>816</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>45642</v>
+        <v>45640</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -1411,13 +1411,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>45642</v>
+        <v>45640</v>
       </c>
       <c r="C72" s="2">
-        <v>1096</v>
+        <v>2</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1425,10 +1425,10 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>45604</v>
+        <v>45641</v>
       </c>
       <c r="C73" s="2">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1439,10 +1439,10 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45604</v>
+        <v>45641</v>
       </c>
       <c r="C74" s="2">
-        <v>789</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1453,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45605</v>
+        <v>45604</v>
       </c>
       <c r="C75" s="2">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,7 +1470,7 @@
         <v>45606</v>
       </c>
       <c r="C76" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1481,13 +1481,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45607</v>
+        <v>45606</v>
       </c>
       <c r="C77" s="2">
-        <v>904</v>
+        <v>26</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,10 +1498,10 @@
         <v>45609</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,10 +1509,10 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45616</v>
+        <v>45610</v>
       </c>
       <c r="C79" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>6</v>
@@ -1523,13 +1523,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45619</v>
+        <v>45612</v>
       </c>
       <c r="C80" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1537,13 +1537,13 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45622</v>
+        <v>45613</v>
       </c>
       <c r="C81" s="2">
-        <v>1</v>
+        <v>217</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1551,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45622</v>
+        <v>45614</v>
       </c>
       <c r="C82" s="2">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,13 +1565,13 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45623</v>
+        <v>45614</v>
       </c>
       <c r="C83" s="2">
-        <v>61</v>
+        <v>320</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1579,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="C84" s="2">
-        <v>2</v>
+        <v>194</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1593,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C85" s="2">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1607,13 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>45625</v>
+        <v>45616</v>
       </c>
       <c r="C86" s="2">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1621,13 +1621,13 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>45626</v>
+        <v>45617</v>
       </c>
       <c r="C87" s="2">
-        <v>302</v>
+        <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1635,10 +1635,10 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>45627</v>
+        <v>45617</v>
       </c>
       <c r="C88" s="2">
-        <v>61</v>
+        <v>272</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1649,10 +1649,10 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="C89" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>5</v>
@@ -1663,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45628</v>
+        <v>45618</v>
       </c>
       <c r="C90" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>8</v>
@@ -1677,13 +1677,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45629</v>
+        <v>45619</v>
       </c>
       <c r="C91" s="2">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1691,10 +1691,10 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45630</v>
+        <v>45620</v>
       </c>
       <c r="C92" s="2">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>5</v>
@@ -1705,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45630</v>
+        <v>45620</v>
       </c>
       <c r="C93" s="2">
-        <v>416</v>
+        <v>670</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1719,13 +1719,13 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45631</v>
+        <v>45621</v>
       </c>
       <c r="C94" s="2">
-        <v>383</v>
+        <v>5</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1733,13 +1733,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45632</v>
+        <v>45621</v>
       </c>
       <c r="C95" s="2">
-        <v>7</v>
+        <v>529</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1747,13 +1747,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>45632</v>
+        <v>45622</v>
       </c>
       <c r="C96" s="2">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,10 +1761,10 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>45633</v>
+        <v>45623</v>
       </c>
       <c r="C97" s="2">
-        <v>67</v>
+        <v>608</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1775,10 +1775,10 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>45633</v>
+        <v>45624</v>
       </c>
       <c r="C98" s="2">
-        <v>881</v>
+        <v>3</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1789,10 +1789,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>45634</v>
+        <v>45625</v>
       </c>
       <c r="C99" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1803,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>45634</v>
+        <v>45625</v>
       </c>
       <c r="C100" s="2">
-        <v>945</v>
+        <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1817,10 +1817,10 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>45635</v>
+        <v>45627</v>
       </c>
       <c r="C101" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>5</v>
@@ -1831,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="C102" s="2">
-        <v>338</v>
+        <v>31</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,13 +1845,13 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>45638</v>
+        <v>45632</v>
       </c>
       <c r="C103" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1859,10 +1859,10 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="C104" s="2">
-        <v>816</v>
+        <v>4</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1873,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C105" s="2">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1887,13 +1887,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C106" s="2">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,13 +1901,13 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>45641</v>
+        <v>45639</v>
       </c>
       <c r="C107" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1915,10 +1915,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C108" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1929,13 +1929,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45605</v>
+        <v>45641</v>
       </c>
       <c r="C109" s="2">
-        <v>187</v>
+        <v>1165</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1943,13 +1943,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45606</v>
+        <v>45642</v>
       </c>
       <c r="C110" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,10 +1957,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45607</v>
+        <v>45604</v>
       </c>
       <c r="C111" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1971,13 +1971,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45608</v>
+        <v>45604</v>
       </c>
       <c r="C112" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1985,13 +1985,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>45609</v>
+        <v>45604</v>
       </c>
       <c r="C113" s="2">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1999,13 +1999,13 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>45609</v>
+        <v>45607</v>
       </c>
       <c r="C114" s="2">
-        <v>319</v>
+        <v>473</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2013,10 +2013,10 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>45611</v>
+        <v>45608</v>
       </c>
       <c r="C115" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>7</v>
@@ -2027,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>45612</v>
+        <v>45610</v>
       </c>
       <c r="C116" s="2">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,13 +2041,13 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>45612</v>
+        <v>45611</v>
       </c>
       <c r="C117" s="2">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2055,13 +2055,13 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>45614</v>
+        <v>45613</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>468</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2069,13 +2069,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C119" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2083,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>45617</v>
+        <v>45616</v>
       </c>
       <c r="C120" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2097,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C121" s="2">
-        <v>681</v>
+        <v>12</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,13 +2111,13 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>45620</v>
+        <v>45618</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2125,13 +2125,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C123" s="2">
-        <v>802</v>
+        <v>49</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2139,10 +2139,10 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C124" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>6</v>
@@ -2153,13 +2153,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C125" s="2">
-        <v>785</v>
+        <v>26</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45627</v>
+        <v>45622</v>
       </c>
       <c r="C126" s="2">
-        <v>3</v>
+        <v>415</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>5</v>
@@ -2181,13 +2181,13 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C127" s="2">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2195,7 +2195,7 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45629</v>
+        <v>45623</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -2209,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45629</v>
+        <v>45624</v>
       </c>
       <c r="C129" s="2">
-        <v>455</v>
+        <v>7</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2223,13 +2223,13 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45630</v>
+        <v>45624</v>
       </c>
       <c r="C130" s="2">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2237,13 +2237,13 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45630</v>
+        <v>45625</v>
       </c>
       <c r="C131" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2251,13 +2251,13 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45631</v>
+        <v>45625</v>
       </c>
       <c r="C132" s="2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2265,10 +2265,10 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45632</v>
+        <v>45625</v>
       </c>
       <c r="C133" s="2">
-        <v>68</v>
+        <v>935</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>5</v>
@@ -2279,10 +2279,10 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45633</v>
+        <v>45627</v>
       </c>
       <c r="C134" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2293,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C135" s="2">
-        <v>108</v>
+        <v>388</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2307,10 +2307,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>45635</v>
+        <v>45630</v>
       </c>
       <c r="C136" s="2">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2321,10 +2321,10 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>45636</v>
+        <v>45631</v>
       </c>
       <c r="C137" s="2">
-        <v>4</v>
+        <v>376</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2335,13 +2335,13 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C138" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2349,13 +2349,13 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>45638</v>
+        <v>45636</v>
       </c>
       <c r="C139" s="2">
-        <v>66</v>
+        <v>642</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2363,13 +2363,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>45638</v>
+        <v>45637</v>
       </c>
       <c r="C140" s="2">
-        <v>514</v>
+        <v>32</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2377,10 +2377,10 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C141" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>5</v>
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C142" s="2">
-        <v>166</v>
+        <v>807</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2405,13 +2405,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C143" s="2">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2419,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>45641</v>
+        <v>45642</v>
       </c>
       <c r="C144" s="2">
-        <v>802</v>
+        <v>1</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2433,13 +2433,13 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>45597</v>
+        <v>45642</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>1096</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2447,10 +2447,10 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="C146" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>6</v>
@@ -2464,7 +2464,7 @@
         <v>45606</v>
       </c>
       <c r="C147" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2475,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>45606</v>
+        <v>45607</v>
       </c>
       <c r="C148" s="2">
-        <v>549</v>
+        <v>3</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2489,13 +2489,13 @@
         <v>4</v>
       </c>
       <c r="B149" s="2">
-        <v>45606</v>
+        <v>45608</v>
       </c>
       <c r="C149" s="2">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2503,13 +2503,13 @@
         <v>4</v>
       </c>
       <c r="B150" s="2">
-        <v>45607</v>
+        <v>45609</v>
       </c>
       <c r="C150" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,10 +2520,10 @@
         <v>45609</v>
       </c>
       <c r="C151" s="2">
-        <v>186</v>
+        <v>319</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2531,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="2">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="C152" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>6</v>
@@ -2548,7 +2548,7 @@
         <v>45612</v>
       </c>
       <c r="C153" s="2">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2559,10 +2559,10 @@
         <v>4</v>
       </c>
       <c r="B154" s="2">
-        <v>45613</v>
+        <v>45612</v>
       </c>
       <c r="C154" s="2">
-        <v>1</v>
+        <v>614</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>5</v>
@@ -2573,13 +2573,13 @@
         <v>4</v>
       </c>
       <c r="B155" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C155" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>45615</v>
       </c>
       <c r="C156" s="2">
-        <v>3</v>
+        <v>247</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2601,10 +2601,10 @@
         <v>4</v>
       </c>
       <c r="B157" s="2">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="C157" s="2">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2615,13 +2615,13 @@
         <v>4</v>
       </c>
       <c r="B158" s="2">
-        <v>45618</v>
+        <v>45620</v>
       </c>
       <c r="C158" s="2">
-        <v>53</v>
+        <v>681</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2629,10 +2629,10 @@
         <v>4</v>
       </c>
       <c r="B159" s="2">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="C159" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2643,13 +2643,13 @@
         <v>4</v>
       </c>
       <c r="B160" s="2">
-        <v>45619</v>
+        <v>45623</v>
       </c>
       <c r="C160" s="2">
-        <v>163</v>
+        <v>802</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2657,13 +2657,13 @@
         <v>4</v>
       </c>
       <c r="B161" s="2">
-        <v>45620</v>
+        <v>45624</v>
       </c>
       <c r="C161" s="2">
+        <v>156</v>
+      </c>
+      <c r="D161" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2671,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="B162" s="2">
-        <v>45621</v>
+        <v>45626</v>
       </c>
       <c r="C162" s="2">
-        <v>33</v>
+        <v>785</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2685,13 +2685,13 @@
         <v>4</v>
       </c>
       <c r="B163" s="2">
-        <v>45622</v>
+        <v>45627</v>
       </c>
       <c r="C163" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2699,13 +2699,13 @@
         <v>4</v>
       </c>
       <c r="B164" s="2">
-        <v>45623</v>
+        <v>45627</v>
       </c>
       <c r="C164" s="2">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2713,10 +2713,10 @@
         <v>4</v>
       </c>
       <c r="B165" s="2">
-        <v>45624</v>
+        <v>45629</v>
       </c>
       <c r="C165" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2727,13 +2727,13 @@
         <v>4</v>
       </c>
       <c r="B166" s="2">
-        <v>45625</v>
+        <v>45629</v>
       </c>
       <c r="C166" s="2">
-        <v>305</v>
+        <v>455</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2741,10 +2741,10 @@
         <v>4</v>
       </c>
       <c r="B167" s="2">
-        <v>45626</v>
+        <v>45630</v>
       </c>
       <c r="C167" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2755,13 +2755,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="2">
-        <v>45626</v>
+        <v>45630</v>
       </c>
       <c r="C168" s="2">
-        <v>757</v>
+        <v>34</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2769,13 +2769,13 @@
         <v>4</v>
       </c>
       <c r="B169" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C169" s="2">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2783,10 +2783,10 @@
         <v>4</v>
       </c>
       <c r="B170" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C170" s="2">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2797,10 +2797,10 @@
         <v>4</v>
       </c>
       <c r="B171" s="2">
-        <v>45629</v>
+        <v>45633</v>
       </c>
       <c r="C171" s="2">
-        <v>384</v>
+        <v>6</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>5</v>
@@ -2811,13 +2811,13 @@
         <v>4</v>
       </c>
       <c r="B172" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C172" s="2">
-        <v>893</v>
+        <v>108</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2825,13 +2825,13 @@
         <v>4</v>
       </c>
       <c r="B173" s="2">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="C173" s="2">
-        <v>711</v>
+        <v>54</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2839,13 +2839,13 @@
         <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="C174" s="2">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2853,13 +2853,13 @@
         <v>4</v>
       </c>
       <c r="B175" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C175" s="2">
-        <v>504</v>
+        <v>28</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2867,13 +2867,13 @@
         <v>4</v>
       </c>
       <c r="B176" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C176" s="2">
-        <v>735</v>
+        <v>66</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2881,13 +2881,13 @@
         <v>4</v>
       </c>
       <c r="B177" s="2">
-        <v>45636</v>
+        <v>45638</v>
       </c>
       <c r="C177" s="2">
-        <v>63</v>
+        <v>514</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2895,13 +2895,13 @@
         <v>4</v>
       </c>
       <c r="B178" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C178" s="2">
-        <v>714</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2909,10 +2909,10 @@
         <v>4</v>
       </c>
       <c r="B179" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C179" s="2">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>6</v>
@@ -2926,7 +2926,7 @@
         <v>45641</v>
       </c>
       <c r="C180" s="2">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2937,13 +2937,13 @@
         <v>4</v>
       </c>
       <c r="B181" s="2">
-        <v>45642</v>
+        <v>45641</v>
       </c>
       <c r="C181" s="2">
-        <v>83</v>
+        <v>802</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>45605</v>
       </c>
       <c r="C182" s="2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2965,10 +2965,10 @@
         <v>4</v>
       </c>
       <c r="B183" s="2">
-        <v>45606</v>
+        <v>45605</v>
       </c>
       <c r="C183" s="2">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>7</v>
@@ -2982,7 +2982,7 @@
         <v>45607</v>
       </c>
       <c r="C184" s="2">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>5</v>
@@ -2996,7 +2996,7 @@
         <v>45608</v>
       </c>
       <c r="C185" s="2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>5</v>
@@ -3007,13 +3007,13 @@
         <v>4</v>
       </c>
       <c r="B186" s="2">
-        <v>45609</v>
+        <v>45608</v>
       </c>
       <c r="C186" s="2">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>45610</v>
       </c>
       <c r="C187" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3035,13 +3035,13 @@
         <v>4</v>
       </c>
       <c r="B188" s="2">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="C188" s="2">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3052,10 +3052,10 @@
         <v>45612</v>
       </c>
       <c r="C189" s="2">
-        <v>208</v>
+        <v>4</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>45613</v>
       </c>
       <c r="C190" s="2">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>5</v>
@@ -3077,10 +3077,10 @@
         <v>4</v>
       </c>
       <c r="B191" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C191" s="2">
-        <v>606</v>
+        <v>2</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3091,13 +3091,13 @@
         <v>4</v>
       </c>
       <c r="B192" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C192" s="2">
-        <v>17</v>
+        <v>236</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3105,13 +3105,13 @@
         <v>4</v>
       </c>
       <c r="B193" s="2">
-        <v>45616</v>
+        <v>45614</v>
       </c>
       <c r="C193" s="2">
-        <v>317</v>
+        <v>45</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3122,10 +3122,10 @@
         <v>45616</v>
       </c>
       <c r="C194" s="2">
-        <v>202</v>
+        <v>33</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="B195" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C195" s="2">
-        <v>779</v>
+        <v>3</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3147,10 +3147,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C196" s="2">
-        <v>719</v>
+        <v>209</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>8</v>
@@ -3161,10 +3161,10 @@
         <v>4</v>
       </c>
       <c r="B197" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C197" s="2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>6</v>
@@ -3175,10 +3175,10 @@
         <v>4</v>
       </c>
       <c r="B198" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C198" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>5</v>
@@ -3189,13 +3189,13 @@
         <v>4</v>
       </c>
       <c r="B199" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C199" s="2">
-        <v>560</v>
+        <v>770</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3203,13 +3203,13 @@
         <v>4</v>
       </c>
       <c r="B200" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C200" s="2">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3217,13 +3217,13 @@
         <v>4</v>
       </c>
       <c r="B201" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C201" s="2">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3231,10 +3231,10 @@
         <v>4</v>
       </c>
       <c r="B202" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C202" s="2">
-        <v>3</v>
+        <v>480</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>5</v>
@@ -3245,13 +3245,13 @@
         <v>4</v>
       </c>
       <c r="B203" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C203" s="2">
-        <v>1117</v>
+        <v>1</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3259,10 +3259,10 @@
         <v>4</v>
       </c>
       <c r="B204" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C204" s="2">
-        <v>3</v>
+        <v>583</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3273,13 +3273,13 @@
         <v>4</v>
       </c>
       <c r="B205" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C205" s="2">
-        <v>128</v>
+        <v>637</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3290,10 +3290,10 @@
         <v>45628</v>
       </c>
       <c r="C206" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3301,13 +3301,13 @@
         <v>4</v>
       </c>
       <c r="B207" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C207" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3315,10 +3315,10 @@
         <v>4</v>
       </c>
       <c r="B208" s="2">
-        <v>45629</v>
+        <v>45634</v>
       </c>
       <c r="C208" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>5</v>
@@ -3329,13 +3329,13 @@
         <v>4</v>
       </c>
       <c r="B209" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C209" s="2">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3343,10 +3343,10 @@
         <v>4</v>
       </c>
       <c r="B210" s="2">
-        <v>45631</v>
+        <v>45636</v>
       </c>
       <c r="C210" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3357,7 +3357,7 @@
         <v>4</v>
       </c>
       <c r="B211" s="2">
-        <v>45634</v>
+        <v>45637</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
@@ -3371,13 +3371,13 @@
         <v>4</v>
       </c>
       <c r="B212" s="2">
-        <v>45634</v>
+        <v>45637</v>
       </c>
       <c r="C212" s="2">
-        <v>66</v>
+        <v>778</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3385,13 +3385,13 @@
         <v>4</v>
       </c>
       <c r="B213" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C213" s="2">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3399,10 +3399,10 @@
         <v>4</v>
       </c>
       <c r="B214" s="2">
-        <v>45636</v>
+        <v>45640</v>
       </c>
       <c r="C214" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>5</v>
@@ -3413,10 +3413,10 @@
         <v>4</v>
       </c>
       <c r="B215" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C215" s="2">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3427,13 +3427,13 @@
         <v>4</v>
       </c>
       <c r="B216" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C216" s="2">
-        <v>29</v>
+        <v>1649</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3441,10 +3441,10 @@
         <v>4</v>
       </c>
       <c r="B217" s="2">
-        <v>45639</v>
+        <v>45642</v>
       </c>
       <c r="C217" s="2">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3455,13 +3455,13 @@
         <v>4</v>
       </c>
       <c r="B218" s="2">
-        <v>45641</v>
+        <v>45597</v>
       </c>
       <c r="C218" s="2">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3469,13 +3469,13 @@
         <v>4</v>
       </c>
       <c r="B219" s="2">
-        <v>45642</v>
+        <v>45604</v>
       </c>
       <c r="C219" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3483,10 +3483,10 @@
         <v>4</v>
       </c>
       <c r="B220" s="2">
-        <v>45642</v>
+        <v>45606</v>
       </c>
       <c r="C220" s="2">
-        <v>602</v>
+        <v>3</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3497,10 +3497,10 @@
         <v>4</v>
       </c>
       <c r="B221" s="2">
-        <v>45604</v>
+        <v>45606</v>
       </c>
       <c r="C221" s="2">
-        <v>2</v>
+        <v>549</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>5</v>
@@ -3511,13 +3511,13 @@
         <v>4</v>
       </c>
       <c r="B222" s="2">
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="C222" s="2">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3525,13 +3525,13 @@
         <v>4</v>
       </c>
       <c r="B223" s="2">
-        <v>45605</v>
+        <v>45607</v>
       </c>
       <c r="C223" s="2">
-        <v>512</v>
+        <v>33</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3539,13 +3539,13 @@
         <v>4</v>
       </c>
       <c r="B224" s="2">
-        <v>45607</v>
+        <v>45609</v>
       </c>
       <c r="C224" s="2">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3553,10 +3553,10 @@
         <v>4</v>
       </c>
       <c r="B225" s="2">
-        <v>45607</v>
+        <v>45610</v>
       </c>
       <c r="C225" s="2">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>7</v>
@@ -3567,10 +3567,10 @@
         <v>4</v>
       </c>
       <c r="B226" s="2">
-        <v>45608</v>
+        <v>45612</v>
       </c>
       <c r="C226" s="2">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>5</v>
@@ -3581,10 +3581,10 @@
         <v>4</v>
       </c>
       <c r="B227" s="2">
-        <v>45611</v>
+        <v>45613</v>
       </c>
       <c r="C227" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3595,13 +3595,13 @@
         <v>4</v>
       </c>
       <c r="B228" s="2">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="C228" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3612,10 +3612,10 @@
         <v>45615</v>
       </c>
       <c r="C229" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3623,13 +3623,13 @@
         <v>4</v>
       </c>
       <c r="B230" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C230" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3637,10 +3637,10 @@
         <v>4</v>
       </c>
       <c r="B231" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C231" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>5</v>
@@ -3651,13 +3651,13 @@
         <v>4</v>
       </c>
       <c r="B232" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C232" s="2">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3665,13 +3665,13 @@
         <v>4</v>
       </c>
       <c r="B233" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C233" s="2">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3679,10 +3679,10 @@
         <v>4</v>
       </c>
       <c r="B234" s="2">
-        <v>45624</v>
+        <v>45620</v>
       </c>
       <c r="C234" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>5</v>
@@ -3693,13 +3693,13 @@
         <v>4</v>
       </c>
       <c r="B235" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C235" s="2">
-        <v>824</v>
+        <v>33</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3707,13 +3707,13 @@
         <v>4</v>
       </c>
       <c r="B236" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C236" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3721,10 +3721,10 @@
         <v>4</v>
       </c>
       <c r="B237" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C237" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>5</v>
@@ -3735,13 +3735,13 @@
         <v>4</v>
       </c>
       <c r="B238" s="2">
-        <v>45627</v>
+        <v>45624</v>
       </c>
       <c r="C238" s="2">
-        <v>786</v>
+        <v>36</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3749,13 +3749,13 @@
         <v>4</v>
       </c>
       <c r="B239" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C239" s="2">
-        <v>160</v>
+        <v>305</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3763,10 +3763,10 @@
         <v>4</v>
       </c>
       <c r="B240" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C240" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>5</v>
@@ -3777,10 +3777,10 @@
         <v>4</v>
       </c>
       <c r="B241" s="2">
-        <v>45629</v>
+        <v>45626</v>
       </c>
       <c r="C241" s="2">
-        <v>40</v>
+        <v>757</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>5</v>
@@ -3791,13 +3791,13 @@
         <v>4</v>
       </c>
       <c r="B242" s="2">
-        <v>45630</v>
+        <v>45628</v>
       </c>
       <c r="C242" s="2">
-        <v>485</v>
+        <v>70</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3805,13 +3805,13 @@
         <v>4</v>
       </c>
       <c r="B243" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C243" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3819,10 +3819,10 @@
         <v>4</v>
       </c>
       <c r="B244" s="2">
-        <v>45631</v>
+        <v>45629</v>
       </c>
       <c r="C244" s="2">
-        <v>4</v>
+        <v>384</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -3833,10 +3833,10 @@
         <v>4</v>
       </c>
       <c r="B245" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C245" s="2">
-        <v>3</v>
+        <v>893</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>5</v>
@@ -3847,10 +3847,10 @@
         <v>4</v>
       </c>
       <c r="B246" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C246" s="2">
-        <v>1404</v>
+        <v>711</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>8</v>
@@ -3864,7 +3864,7 @@
         <v>45633</v>
       </c>
       <c r="C247" s="2">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>7</v>
@@ -3875,10 +3875,10 @@
         <v>4</v>
       </c>
       <c r="B248" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C248" s="2">
-        <v>10</v>
+        <v>504</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>5</v>
@@ -3889,13 +3889,13 @@
         <v>4</v>
       </c>
       <c r="B249" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C249" s="2">
-        <v>854</v>
+        <v>735</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3906,10 +3906,10 @@
         <v>45636</v>
       </c>
       <c r="C250" s="2">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3917,13 +3917,13 @@
         <v>4</v>
       </c>
       <c r="B251" s="2">
-        <v>45636</v>
+        <v>45638</v>
       </c>
       <c r="C251" s="2">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3931,13 +3931,13 @@
         <v>4</v>
       </c>
       <c r="B252" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C252" s="2">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3945,10 +3945,10 @@
         <v>4</v>
       </c>
       <c r="B253" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C253" s="2">
-        <v>535</v>
+        <v>3</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>5</v>
@@ -3959,13 +3959,13 @@
         <v>4</v>
       </c>
       <c r="B254" s="2">
-        <v>45640</v>
+        <v>45642</v>
       </c>
       <c r="C254" s="2">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3973,10 +3973,10 @@
         <v>4</v>
       </c>
       <c r="B255" s="2">
-        <v>45640</v>
+        <v>45605</v>
       </c>
       <c r="C255" s="2">
-        <v>829</v>
+        <v>17</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>5</v>
@@ -3987,13 +3987,13 @@
         <v>4</v>
       </c>
       <c r="B256" s="2">
-        <v>45641</v>
+        <v>45606</v>
       </c>
       <c r="C256" s="2">
-        <v>2</v>
+        <v>211</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4001,13 +4001,13 @@
         <v>4</v>
       </c>
       <c r="B257" s="2">
-        <v>45641</v>
+        <v>45607</v>
       </c>
       <c r="C257" s="2">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4015,10 +4015,10 @@
         <v>4</v>
       </c>
       <c r="B258" s="2">
-        <v>45605</v>
+        <v>45608</v>
       </c>
       <c r="C258" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>5</v>
@@ -4029,10 +4029,10 @@
         <v>4</v>
       </c>
       <c r="B259" s="2">
-        <v>45605</v>
+        <v>45609</v>
       </c>
       <c r="C259" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>6</v>
@@ -4043,10 +4043,10 @@
         <v>4</v>
       </c>
       <c r="B260" s="2">
-        <v>45607</v>
+        <v>45610</v>
       </c>
       <c r="C260" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>5</v>
@@ -4057,10 +4057,10 @@
         <v>4</v>
       </c>
       <c r="B261" s="2">
-        <v>45608</v>
+        <v>45610</v>
       </c>
       <c r="C261" s="2">
-        <v>3</v>
+        <v>237</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>5</v>
@@ -4071,13 +4071,13 @@
         <v>4</v>
       </c>
       <c r="B262" s="2">
-        <v>45608</v>
+        <v>45612</v>
       </c>
       <c r="C262" s="2">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4085,10 +4085,10 @@
         <v>4</v>
       </c>
       <c r="B263" s="2">
-        <v>45610</v>
+        <v>45613</v>
       </c>
       <c r="C263" s="2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>5</v>
@@ -4099,13 +4099,13 @@
         <v>4</v>
       </c>
       <c r="B264" s="2">
-        <v>45611</v>
+        <v>45613</v>
       </c>
       <c r="C264" s="2">
-        <v>2</v>
+        <v>606</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4113,13 +4113,13 @@
         <v>4</v>
       </c>
       <c r="B265" s="2">
-        <v>45612</v>
+        <v>45615</v>
       </c>
       <c r="C265" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4127,10 +4127,10 @@
         <v>4</v>
       </c>
       <c r="B266" s="2">
-        <v>45613</v>
+        <v>45616</v>
       </c>
       <c r="C266" s="2">
-        <v>32</v>
+        <v>317</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>5</v>
@@ -4141,13 +4141,13 @@
         <v>4</v>
       </c>
       <c r="B267" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C267" s="2">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4155,13 +4155,13 @@
         <v>4</v>
       </c>
       <c r="B268" s="2">
-        <v>45614</v>
+        <v>45619</v>
       </c>
       <c r="C268" s="2">
-        <v>236</v>
+        <v>779</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4169,13 +4169,13 @@
         <v>4</v>
       </c>
       <c r="B269" s="2">
-        <v>45614</v>
+        <v>45619</v>
       </c>
       <c r="C269" s="2">
-        <v>45</v>
+        <v>719</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4183,13 +4183,13 @@
         <v>4</v>
       </c>
       <c r="B270" s="2">
-        <v>45616</v>
+        <v>45620</v>
       </c>
       <c r="C270" s="2">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4197,7 +4197,7 @@
         <v>4</v>
       </c>
       <c r="B271" s="2">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="C271" s="2">
         <v>3</v>
@@ -4211,10 +4211,10 @@
         <v>4</v>
       </c>
       <c r="B272" s="2">
-        <v>45617</v>
+        <v>45622</v>
       </c>
       <c r="C272" s="2">
-        <v>209</v>
+        <v>560</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>8</v>
@@ -4225,13 +4225,13 @@
         <v>4</v>
       </c>
       <c r="B273" s="2">
-        <v>45617</v>
+        <v>45623</v>
       </c>
       <c r="C273" s="2">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4239,13 +4239,13 @@
         <v>4</v>
       </c>
       <c r="B274" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C274" s="2">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4253,10 +4253,10 @@
         <v>4</v>
       </c>
       <c r="B275" s="2">
-        <v>45618</v>
+        <v>45625</v>
       </c>
       <c r="C275" s="2">
-        <v>770</v>
+        <v>3</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>5</v>
@@ -4267,13 +4267,13 @@
         <v>4</v>
       </c>
       <c r="B276" s="2">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="C276" s="2">
-        <v>298</v>
+        <v>1117</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4281,10 +4281,10 @@
         <v>4</v>
       </c>
       <c r="B277" s="2">
-        <v>45621</v>
+        <v>45626</v>
       </c>
       <c r="C277" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>5</v>
@@ -4295,13 +4295,13 @@
         <v>4</v>
       </c>
       <c r="B278" s="2">
-        <v>45621</v>
+        <v>45626</v>
       </c>
       <c r="C278" s="2">
-        <v>480</v>
+        <v>128</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4309,10 +4309,10 @@
         <v>4</v>
       </c>
       <c r="B279" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C279" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>5</v>
@@ -4323,10 +4323,10 @@
         <v>4</v>
       </c>
       <c r="B280" s="2">
-        <v>45624</v>
+        <v>45628</v>
       </c>
       <c r="C280" s="2">
-        <v>583</v>
+        <v>33</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>5</v>
@@ -4337,10 +4337,10 @@
         <v>4</v>
       </c>
       <c r="B281" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C281" s="2">
-        <v>637</v>
+        <v>4</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>5</v>
@@ -4351,13 +4351,13 @@
         <v>4</v>
       </c>
       <c r="B282" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C282" s="2">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4368,10 +4368,10 @@
         <v>45631</v>
       </c>
       <c r="C283" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>45634</v>
       </c>
       <c r="C284" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>5</v>
@@ -4396,10 +4396,10 @@
         <v>45634</v>
       </c>
       <c r="C285" s="2">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4407,13 +4407,13 @@
         <v>4</v>
       </c>
       <c r="B286" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C286" s="2">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4421,10 +4421,10 @@
         <v>4</v>
       </c>
       <c r="B287" s="2">
-        <v>45637</v>
+        <v>45636</v>
       </c>
       <c r="C287" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>5</v>
@@ -4438,10 +4438,10 @@
         <v>45637</v>
       </c>
       <c r="C288" s="2">
-        <v>778</v>
+        <v>64</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4449,13 +4449,13 @@
         <v>4</v>
       </c>
       <c r="B289" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C289" s="2">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4463,10 +4463,10 @@
         <v>4</v>
       </c>
       <c r="B290" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C290" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>5</v>
@@ -4477,13 +4477,13 @@
         <v>4</v>
       </c>
       <c r="B291" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C291" s="2">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4491,13 +4491,13 @@
         <v>4</v>
       </c>
       <c r="B292" s="2">
-        <v>45640</v>
+        <v>45642</v>
       </c>
       <c r="C292" s="2">
-        <v>1649</v>
+        <v>6</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>45642</v>
       </c>
       <c r="C293" s="2">
-        <v>71</v>
+        <v>602</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>5</v>
